--- a/哈蜜瓜收支表.xlsx
+++ b/哈蜜瓜收支表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2513128\Desktop\Melon Finance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB6D791F-84CF-448E-9AD5-A82126E1DCEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7B3CC10-A5B4-4361-A54A-C865E82B115B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,9 +37,6 @@
     <t>項目</t>
   </si>
   <si>
-    <t>$</t>
-  </si>
-  <si>
     <t>經手人</t>
   </si>
   <si>
@@ -105,6 +102,10 @@
   </si>
   <si>
     <t>力玄</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>金額</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -113,7 +114,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -153,7 +154,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -473,13 +474,13 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -487,16 +488,16 @@
         <v>46266</v>
       </c>
       <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
         <v>6</v>
-      </c>
-      <c r="C2" t="s">
-        <v>7</v>
       </c>
       <c r="D2">
         <v>1520</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -504,16 +505,16 @@
         <v>46266</v>
       </c>
       <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
         <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
       </c>
       <c r="D3">
         <v>3750</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -521,16 +522,16 @@
         <v>46273</v>
       </c>
       <c r="B4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s">
         <v>6</v>
-      </c>
-      <c r="C4" t="s">
-        <v>7</v>
       </c>
       <c r="D4">
         <v>1520</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -538,19 +539,19 @@
         <v>46273</v>
       </c>
       <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" t="s">
         <v>9</v>
-      </c>
-      <c r="C5" t="s">
-        <v>10</v>
       </c>
       <c r="D5">
         <v>2900</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -558,16 +559,16 @@
         <v>46280</v>
       </c>
       <c r="B6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
         <v>6</v>
-      </c>
-      <c r="C6" t="s">
-        <v>7</v>
       </c>
       <c r="D6">
         <v>1520</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -575,16 +576,16 @@
         <v>46280</v>
       </c>
       <c r="B7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" t="s">
         <v>9</v>
-      </c>
-      <c r="C7" t="s">
-        <v>10</v>
       </c>
       <c r="D7">
         <v>2500</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -592,19 +593,19 @@
         <v>46281</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D8">
         <v>2200</v>
       </c>
       <c r="E8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -612,16 +613,16 @@
         <v>46287</v>
       </c>
       <c r="B9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" t="s">
         <v>6</v>
-      </c>
-      <c r="C9" t="s">
-        <v>7</v>
       </c>
       <c r="D9">
         <v>760</v>
       </c>
       <c r="E9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -629,16 +630,16 @@
         <v>46287</v>
       </c>
       <c r="B10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" t="s">
         <v>9</v>
-      </c>
-      <c r="C10" t="s">
-        <v>10</v>
       </c>
       <c r="D10">
         <v>500</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -646,16 +647,16 @@
         <v>46294</v>
       </c>
       <c r="B11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" t="s">
         <v>6</v>
-      </c>
-      <c r="C11" t="s">
-        <v>7</v>
       </c>
       <c r="D11">
         <v>1520</v>
       </c>
       <c r="E11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -663,19 +664,19 @@
         <v>46294</v>
       </c>
       <c r="B12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" t="s">
         <v>9</v>
-      </c>
-      <c r="C12" t="s">
-        <v>10</v>
       </c>
       <c r="D12">
         <v>2550</v>
       </c>
       <c r="E12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -683,16 +684,16 @@
         <v>46294</v>
       </c>
       <c r="B13" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D13">
         <v>990</v>
       </c>
       <c r="E13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -711,21 +712,21 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" t="s">
         <v>18</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>19</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>20</v>
-      </c>
-      <c r="D1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B2" s="1">
         <v>46282</v>
@@ -739,7 +740,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B3" s="1">
         <v>46259</v>
@@ -753,7 +754,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B4" s="1">
         <v>46287</v>
@@ -767,7 +768,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B5" s="1">
         <v>46301</v>

--- a/哈蜜瓜收支表.xlsx
+++ b/哈蜜瓜收支表.xlsx
@@ -1,140 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2513128\Desktop\Melon Finance\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7B3CC10-A5B4-4361-A54A-C865E82B115B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="收支明細" sheetId="1" r:id="rId1"/>
-    <sheet name="季繳名單" sheetId="2" r:id="rId2"/>
+    <sheet name="收支明細" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="季繳名單" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="26">
-  <si>
-    <t>日期</t>
-  </si>
-  <si>
-    <t>類別</t>
-  </si>
-  <si>
-    <t>項目</t>
-  </si>
-  <si>
-    <t>經手人</t>
-  </si>
-  <si>
-    <t>備註</t>
-  </si>
-  <si>
-    <t>支出</t>
-  </si>
-  <si>
-    <t>場地費</t>
-  </si>
-  <si>
-    <t>齊</t>
-  </si>
-  <si>
-    <t>收入</t>
-  </si>
-  <si>
-    <t>臨打</t>
-  </si>
-  <si>
-    <t>櫃台</t>
-  </si>
-  <si>
-    <t>妙</t>
-  </si>
-  <si>
-    <t>1hr*1</t>
-  </si>
-  <si>
-    <t>季繳</t>
-  </si>
-  <si>
-    <t>轉帳 (冠臻)</t>
-  </si>
-  <si>
-    <t>1hr*2</t>
-  </si>
-  <si>
-    <t>羽毛球</t>
-  </si>
-  <si>
-    <t>姓名</t>
-  </si>
-  <si>
-    <t>繳費日期</t>
-  </si>
-  <si>
-    <t>季繳開始日期</t>
-  </si>
-  <si>
-    <t>剩餘次數</t>
-  </si>
-  <si>
-    <t>冠臻</t>
-  </si>
-  <si>
-    <t>林小君</t>
-  </si>
-  <si>
-    <t>阿強</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>力玄</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>金額</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="新細明體"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="新細明體"/>
-      <family val="3"/>
-      <charset val="136"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -153,22 +51,81 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="一般" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -456,332 +413,543 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F13"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>類別</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>金額</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>經手人</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>備註</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
         <v>46266</v>
       </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>支出</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>場地費</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
         <v>1520</v>
       </c>
-      <c r="E2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>齊</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
         <v>46266</v>
       </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>收入</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>臨打</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
         <v>3750</v>
       </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>櫃台</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
         <v>46273</v>
       </c>
-      <c r="B4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>支出</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>場地費</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
         <v>1520</v>
       </c>
-      <c r="E4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>妙</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
         <v>46273</v>
       </c>
-      <c r="B5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>收入</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>臨打</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
         <v>2900</v>
       </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>櫃台</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1hr*1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
         <v>46280</v>
       </c>
-      <c r="B6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>支出</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>場地費</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
         <v>1520</v>
       </c>
-      <c r="E6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>妙</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
         <v>46280</v>
       </c>
-      <c r="B7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>收入</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>臨打</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
         <v>2500</v>
       </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>櫃台</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
         <v>46281</v>
       </c>
-      <c r="B8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>收入</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>季繳</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
         <v>2200</v>
       </c>
-      <c r="E8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>妙</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>轉帳 (冠臻)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
         <v>46287</v>
       </c>
-      <c r="B9" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>支出</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>場地費</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
         <v>760</v>
       </c>
-      <c r="E9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>妙</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
         <v>46287</v>
       </c>
-      <c r="B10" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>收入</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>臨打</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
         <v>500</v>
       </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>櫃台</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
         <v>46294</v>
       </c>
-      <c r="B11" t="s">
-        <v>5</v>
-      </c>
-      <c r="C11" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>支出</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>場地費</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
         <v>1520</v>
       </c>
-      <c r="E11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>妙</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
         <v>46294</v>
       </c>
-      <c r="B12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>收入</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>臨打</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
         <v>2550</v>
       </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>櫃台</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>1hr*2</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
         <v>46294</v>
       </c>
-      <c r="B13" t="s">
-        <v>5</v>
-      </c>
-      <c r="C13" t="s">
-        <v>16</v>
-      </c>
-      <c r="D13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>支出</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>羽毛球</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
         <v>990</v>
       </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>櫃台</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>收入</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>臨打</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>2750</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>櫃台</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>支出</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>場地費</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1520</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>櫃台</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>支出</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>羽毛球</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>610</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>櫃台</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>收入</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>季繳</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>2200</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>齊</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="3" width="20" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2" s="1">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>姓名</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>繳費日期</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>季繳開始日期</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>剩餘次數</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>冠臻</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="n">
         <v>46282</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2" s="1" t="n">
         <v>46280</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" s="1">
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>林小君</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="n">
         <v>46259</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3" s="1" t="n">
         <v>46266</v>
       </c>
-      <c r="D3">
+      <c r="D3" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" s="1">
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>阿強</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="n">
         <v>46287</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4" s="1" t="n">
         <v>46287</v>
       </c>
-      <c r="D4">
+      <c r="D4" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" s="1">
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>力玄</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="n">
         <v>46301</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5" s="1" t="n">
         <v>46301</v>
       </c>
-      <c r="D5">
+      <c r="D5" t="n">
         <v>9</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/哈蜜瓜收支表.xlsx
+++ b/哈蜜瓜收支表.xlsx
@@ -455,20 +455,20 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46266</v>
+        <v>46301</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>支出</t>
+          <t>收入</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>場地費</t>
+          <t>季繳</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1520</v>
+        <v>2200</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -479,7 +479,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46266</v>
+        <v>46301</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -492,7 +492,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3750</v>
+        <v>2750</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -503,7 +503,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46273</v>
+        <v>46301</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -520,79 +520,79 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>妙</t>
+          <t>櫃台</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46273</v>
+        <v>46294</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>收入</t>
+          <t>支出</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>臨打</t>
+          <t>場地費</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2900</v>
+        <v>1520</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>櫃台</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>1hr*1</t>
-        </is>
-      </c>
+          <t>妙</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46280</v>
+        <v>46294</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>支出</t>
+          <t>收入</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>場地費</t>
+          <t>臨打</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1520</v>
+        <v>2550</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>妙</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
+          <t>櫃台</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1hr*2</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46280</v>
+        <v>46294</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>收入</t>
+          <t>支出</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>臨打</t>
+          <t>羽毛球</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2500</v>
+        <v>990</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -603,31 +603,27 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46281</v>
+        <v>46287</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>收入</t>
+          <t>支出</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>季繳</t>
+          <t>場地費</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2200</v>
+        <v>760</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>妙</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>轉帳 (冠臻)</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -635,27 +631,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>支出</t>
+          <t>收入</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>場地費</t>
+          <t>臨打</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>760</v>
+        <v>500</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>妙</t>
+          <t>櫃台</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46287</v>
+        <v>46281</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -664,22 +660,26 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>臨打</t>
+          <t>季繳</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>500</v>
+        <v>2200</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>櫃台</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
+          <t>妙</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>轉帳 (冠臻)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46294</v>
+        <v>46280</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46294</v>
+        <v>46280</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -716,22 +716,18 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2550</v>
+        <v>2500</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>櫃台</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>1hr*2</t>
-        </is>
-      </c>
+      <c r="F12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46294</v>
+        <v>46273</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -740,22 +736,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>羽毛球</t>
+          <t>場地費</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>990</v>
+        <v>1520</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>櫃台</t>
+          <t>妙</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46301</v>
+        <v>46273</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -768,18 +764,22 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2750</v>
+        <v>2900</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>櫃台</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1hr*1</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46301</v>
+        <v>46266</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -796,27 +796,27 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>櫃台</t>
+          <t>齊</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46301</v>
+        <v>46266</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>支出</t>
+          <t>收入</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>羽毛球</t>
+          <t>臨打</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>610</v>
+        <v>3750</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -827,24 +827,24 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46302</v>
+        <v>46301</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>收入</t>
+          <t>支出</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>季繳</t>
+          <t>羽毛球</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2200</v>
+        <v>610</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>齊</t>
+          <t>櫃台</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>

--- a/哈蜜瓜收支表.xlsx
+++ b/哈蜜瓜收支表.xlsx
@@ -475,7 +475,11 @@
           <t>齊</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>力玄</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -527,7 +531,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46294</v>
+        <v>46301</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -536,15 +540,15 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>場地費</t>
+          <t>羽毛球</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1520</v>
+        <v>610</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>妙</t>
+          <t>櫃台</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -555,27 +559,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>收入</t>
+          <t>支出</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>臨打</t>
+          <t>場地費</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2550</v>
+        <v>1520</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>櫃台</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>1hr*2</t>
-        </is>
-      </c>
+          <t>妙</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -583,27 +583,31 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>支出</t>
+          <t>收入</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>羽毛球</t>
+          <t>臨打</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>990</v>
+        <v>2550</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>櫃台</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1hr*2</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46287</v>
+        <v>46294</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -612,15 +616,15 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>場地費</t>
+          <t>羽毛球</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>760</v>
+        <v>990</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>妙</t>
+          <t>櫃台</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -631,27 +635,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>收入</t>
+          <t>支出</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>臨打</t>
+          <t>場地費</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>500</v>
+        <v>760</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>櫃台</t>
+          <t>妙</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46281</v>
+        <v>46287</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -660,46 +664,46 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>季繳</t>
+          <t>臨打</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2200</v>
+        <v>500</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>妙</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>轉帳 (冠臻)</t>
-        </is>
-      </c>
+          <t>櫃台</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>支出</t>
+          <t>收入</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>場地費</t>
+          <t>季繳</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1520</v>
+        <v>2200</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>妙</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>轉帳 (冠臻)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -707,44 +711,44 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>收入</t>
+          <t>支出</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>臨打</t>
+          <t>場地費</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2500</v>
+        <v>1520</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>櫃台</t>
+          <t>妙</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46273</v>
+        <v>46280</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>支出</t>
+          <t>收入</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>場地費</t>
+          <t>臨打</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1520</v>
+        <v>2500</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>妙</t>
+          <t>櫃台</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -755,51 +759,51 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>收入</t>
+          <t>支出</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>臨打</t>
+          <t>場地費</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2900</v>
+        <v>1520</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>櫃台</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>1hr*1</t>
-        </is>
-      </c>
+          <t>妙</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46266</v>
+        <v>46273</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>支出</t>
+          <t>收入</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>場地費</t>
+          <t>臨打</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1520</v>
+        <v>2900</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>齊</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
+          <t>櫃台</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>1hr*1</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -807,40 +811,40 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>收入</t>
+          <t>支出</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>臨打</t>
+          <t>場地費</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3750</v>
+        <v>1520</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>櫃台</t>
+          <t>齊</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46301</v>
+        <v>46266</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>支出</t>
+          <t>收入</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>羽毛球</t>
+          <t>臨打</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>610</v>
+        <v>3750</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>

--- a/哈蜜瓜收支表.xlsx
+++ b/哈蜜瓜收支表.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -852,6 +852,78 @@
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>收入</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>臨打</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>2130</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>櫃台</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>支出</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>場地費</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>2280</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>櫃台</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>支出</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>羽毛球</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>610</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>櫃台</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -902,7 +974,7 @@
         <v>46280</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -918,7 +990,7 @@
         <v>46266</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -934,7 +1006,7 @@
         <v>46287</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -950,7 +1022,7 @@
         <v>46301</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/哈蜜瓜收支表.xlsx
+++ b/哈蜜瓜收支表.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -924,6 +924,34 @@
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>收入</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>24070</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>妙</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>現金結算 (校正)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/哈蜜瓜收支表.xlsx
+++ b/哈蜜瓜收支表.xlsx
@@ -17,10 +17,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -50,9 +47,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -454,8 +450,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
-        <v>46301</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -464,74 +462,80 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>季繳</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2200</v>
+        <v>24070</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>齊</t>
+          <t>妙</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>力玄</t>
+          <t>現金結算 (校正)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>46301</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>支出</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>場地費</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2280</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>櫃台</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>收入</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>臨打</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>2750</v>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="D4" t="n">
+        <v>2130</v>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t>櫃台</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>支出</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>場地費</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>1520</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>櫃台</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>46301</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -554,404 +558,436 @@
       <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>46294</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>收入</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>臨打</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2750</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>櫃台</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>收入</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>季繳</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2200</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>齊</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>力玄</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>支出</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>羽毛球</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>610</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>櫃台</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>支出</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>場地費</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D9" t="n">
         <v>1520</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>櫃台</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>收入</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>臨打</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2550</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>櫃台</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1hr*2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>支出</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>場地費</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1520</v>
+      </c>
+      <c r="E11" t="inlineStr">
         <is>
           <t>妙</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="B7" t="inlineStr">
+      <c r="F11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>支出</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>羽毛球</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>990</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>櫃台</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>支出</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>場地費</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>760</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>妙</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
         <is>
           <t>收入</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>臨打</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>2550</v>
-      </c>
-      <c r="E7" t="inlineStr">
+      <c r="D14" t="n">
+        <v>500</v>
+      </c>
+      <c r="E14" t="inlineStr">
         <is>
           <t>櫃台</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>1hr*2</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="B8" t="inlineStr">
+      <c r="F14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>收入</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>季繳</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>2200</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>妙</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>轉帳 (冠臻)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>收入</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>臨打</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>2500</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>櫃台</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
         <is>
           <t>支出</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>羽毛球</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>990</v>
-      </c>
-      <c r="E8" t="inlineStr">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>場地費</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1520</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>妙</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>支出</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>場地費</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1520</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>妙</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>收入</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>臨打</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>2900</v>
+      </c>
+      <c r="E19" t="inlineStr">
         <is>
           <t>櫃台</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>46287</v>
-      </c>
-      <c r="B9" t="inlineStr">
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>1hr*1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
         <is>
           <t>支出</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>場地費</t>
         </is>
       </c>
-      <c r="D9" t="n">
-        <v>760</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>妙</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="n">
-        <v>46287</v>
-      </c>
-      <c r="B10" t="inlineStr">
+      <c r="D20" t="n">
+        <v>1520</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>齊</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
         <is>
           <t>收入</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>臨打</t>
         </is>
       </c>
-      <c r="D10" t="n">
-        <v>500</v>
-      </c>
-      <c r="E10" t="inlineStr">
+      <c r="D21" t="n">
+        <v>3750</v>
+      </c>
+      <c r="E21" t="inlineStr">
         <is>
           <t>櫃台</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>收入</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>季繳</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>2200</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>妙</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>轉帳 (冠臻)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>支出</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>場地費</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>1520</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>妙</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>收入</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>臨打</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>2500</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>櫃台</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="n">
-        <v>46273</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>支出</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>場地費</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>1520</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>妙</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="n">
-        <v>46273</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>收入</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>臨打</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>2900</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>櫃台</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>1hr*1</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="n">
-        <v>46266</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>支出</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>場地費</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>1520</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>齊</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n">
-        <v>46266</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>收入</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>臨打</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>3750</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>櫃台</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="n">
-        <v>46308</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>收入</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>臨打</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>2130</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>櫃台</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n">
-        <v>46308</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>支出</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>場地費</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>2280</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>櫃台</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="n">
-        <v>46308</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>支出</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>羽毛球</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>610</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>櫃台</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="n">
-        <v>46309</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>收入</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>24070</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>妙</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>現金結算 (校正)</t>
-        </is>
-      </c>
+      <c r="F21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -995,11 +1031,15 @@
           <t>冠臻</t>
         </is>
       </c>
-      <c r="B2" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="C2" s="1" t="n">
-        <v>46280</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
       </c>
       <c r="D2" t="n">
         <v>5</v>
@@ -1011,11 +1051,15 @@
           <t>林小君</t>
         </is>
       </c>
-      <c r="B3" s="1" t="n">
-        <v>46259</v>
-      </c>
-      <c r="C3" s="1" t="n">
-        <v>46266</v>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
       </c>
       <c r="D3" t="n">
         <v>3</v>
@@ -1027,11 +1071,15 @@
           <t>阿強</t>
         </is>
       </c>
-      <c r="B4" s="1" t="n">
-        <v>46287</v>
-      </c>
-      <c r="C4" s="1" t="n">
-        <v>46287</v>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
       </c>
       <c r="D4" t="n">
         <v>6</v>
@@ -1043,11 +1091,15 @@
           <t>力玄</t>
         </is>
       </c>
-      <c r="B5" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="C5" s="1" t="n">
-        <v>46301</v>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
       </c>
       <c r="D5" t="n">
         <v>8</v>

--- a/哈蜜瓜收支表.xlsx
+++ b/哈蜜瓜收支表.xlsx
@@ -492,11 +492,11 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>場地費</t>
+          <t>羽毛球</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2280</v>
+        <v>610</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -513,16 +513,16 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>收入</t>
+          <t>支出</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>臨打</t>
+          <t>場地費</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2130</v>
+        <v>2280</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -539,16 +539,16 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>支出</t>
+          <t>收入</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>羽毛球</t>
+          <t>臨打</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>610</v>
+        <v>2130</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -673,27 +673,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>收入</t>
+          <t>支出</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>臨打</t>
+          <t>羽毛球</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2550</v>
+        <v>990</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>櫃台</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>1hr*2</t>
-        </is>
-      </c>
+      <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -703,23 +699,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>支出</t>
+          <t>收入</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>場地費</t>
+          <t>臨打</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1520</v>
+        <v>2550</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>妙</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
+          <t>櫃台</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>1hr*2</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -734,15 +734,15 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>羽毛球</t>
+          <t>場地費</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>990</v>
+        <v>1520</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>櫃台</t>
+          <t>妙</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>

--- a/哈蜜瓜收支表.xlsx
+++ b/哈蜜瓜收支表.xlsx
@@ -487,16 +487,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>支出</t>
+          <t>收入</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>羽毛球</t>
+          <t>臨打</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>610</v>
+        <v>2130</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -518,11 +518,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>場地費</t>
+          <t>羽毛球</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2280</v>
+        <v>610</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -539,16 +539,16 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>收入</t>
+          <t>支出</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>臨打</t>
+          <t>場地費</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2130</v>
+        <v>2280</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -678,15 +678,15 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>羽毛球</t>
+          <t>場地費</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>990</v>
+        <v>1520</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>櫃台</t>
+          <t>妙</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -699,27 +699,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>收入</t>
+          <t>支出</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>臨打</t>
+          <t>羽毛球</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2550</v>
+        <v>990</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>櫃台</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>1hr*2</t>
-        </is>
-      </c>
+      <c r="F11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -729,23 +725,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>支出</t>
+          <t>收入</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>場地費</t>
+          <t>臨打</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1520</v>
+        <v>2550</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>妙</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
+          <t>櫃台</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>1hr*2</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">

--- a/哈蜜瓜收支表.xlsx
+++ b/哈蜜瓜收支表.xlsx
@@ -487,16 +487,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>收入</t>
+          <t>支出</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>臨打</t>
+          <t>場地費</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2130</v>
+        <v>2280</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -513,16 +513,16 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>支出</t>
+          <t>收入</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>羽毛球</t>
+          <t>臨打</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>610</v>
+        <v>2130</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -544,11 +544,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>場地費</t>
+          <t>羽毛球</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2280</v>
+        <v>610</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -673,23 +673,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>支出</t>
+          <t>收入</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>場地費</t>
+          <t>臨打</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1520</v>
+        <v>2550</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>妙</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
+          <t>櫃台</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1hr*2</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -704,15 +708,15 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>羽毛球</t>
+          <t>場地費</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>990</v>
+        <v>1520</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>櫃台</t>
+          <t>妙</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -725,27 +729,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>收入</t>
+          <t>支出</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>臨打</t>
+          <t>羽毛球</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2550</v>
+        <v>990</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>櫃台</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>1hr*2</t>
-        </is>
-      </c>
+      <c r="F12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">

--- a/哈蜜瓜收支表.xlsx
+++ b/哈蜜瓜收支表.xlsx
@@ -492,11 +492,11 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>場地費</t>
+          <t>羽毛球</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2280</v>
+        <v>610</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -513,16 +513,16 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>收入</t>
+          <t>支出</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>臨打</t>
+          <t>場地費</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2130</v>
+        <v>2280</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -539,16 +539,16 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>支出</t>
+          <t>收入</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>羽毛球</t>
+          <t>臨打</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>610</v>
+        <v>2130</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -673,27 +673,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>收入</t>
+          <t>支出</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>臨打</t>
+          <t>羽毛球</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2550</v>
+        <v>990</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>櫃台</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>1hr*2</t>
-        </is>
-      </c>
+      <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -703,23 +699,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>支出</t>
+          <t>收入</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>場地費</t>
+          <t>臨打</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1520</v>
+        <v>2550</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>妙</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
+          <t>櫃台</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>1hr*2</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -734,15 +734,15 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>羽毛球</t>
+          <t>場地費</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>990</v>
+        <v>1520</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>櫃台</t>
+          <t>妙</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -1073,16 +1073,16 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
